--- a/Dokumen/Usecase Scenario.xlsx
+++ b/Dokumen/Usecase Scenario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 7\KP\Point-Of-Sale-App\Dokumen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0419E5D5-8626-41EA-9D43-5EE5562CBF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFB95F3-CF0C-4BB8-BCE2-53E213C4BEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="2595" windowWidth="15375" windowHeight="7875" xr2:uid="{6A560D3A-8633-4F17-BD07-72BF298389B9}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{6A560D3A-8633-4F17-BD07-72BF298389B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
   <si>
     <t>1. Use Case: Login &amp; Inisialisasi Kasir</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Klik tombol "Simpan"</t>
   </si>
   <si>
-    <t>Mengirimkan sinyal data terbaru agar saat kasir melakukan request, list menu langsung ter-update.</t>
-  </si>
-  <si>
     <t>6. Use Case: Kelola Kasir</t>
   </si>
   <si>
@@ -222,15 +219,6 @@
     <t>Melakukan CRUD (Menambahkan kasir baru dengan membuatkan id kasir, mengubah data kasir atau menghapus/menonaktifkan akun kasir).</t>
   </si>
   <si>
-    <t>Memvalidasi data (memastikan ID Kasir bersifat unik dan belum pernah digunakan).</t>
-  </si>
-  <si>
-    <t>Menyimpan atau memperbarui data akun kasir ke dalam database.</t>
-  </si>
-  <si>
-    <t>Menampilkan notifikasi bahwa pengelolaan data kasir telah berhasil disimpan.</t>
-  </si>
-  <si>
     <t>7. Use Case: Kelola Transaksi</t>
   </si>
   <si>
@@ -345,44 +333,9 @@
     <t>Kasir Pagi akan pergi istirahat dan menekan tombol "Jeda Sesi / Switch Kasir".</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Mengunci layar transaksi aktif Kasir Pagi dan menampilkan jendela </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pop-up Pin/ID Login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cepat.</t>
-    </r>
-  </si>
-  <si>
     <t>Kasir Siang (pengganti) memasukkan ID Kasir miliknya untuk mengambil alih terminal.</t>
   </si>
   <si>
-    <t>Memverifikasi ID Kasir Siang tanpa memutus/mengubah status shift Kasir Pagi di backend.</t>
-  </si>
-  <si>
-    <t>Membuka layar POS baru. Setiap transaksi yang dicetak mulai detik ini akan ditandai dengan kode kasir_id = Kasir_Siang.</t>
-  </si>
-  <si>
-    <t>(Saat istirahat selesai) Kasir Pagi kembali dan mengulangi proses masuk via ID untuk melanjutkan sesi lamanya yang sempat dijeda.</t>
-  </si>
-  <si>
     <t>11. Use Case: Membatalkan Pemesanan</t>
   </si>
   <si>
@@ -434,9 +387,6 @@
     <t>Memperbarui status log transaksi di database dan mencatat riwayat tindakan koreksi yang dilakukan oleh Admin untuk transparansi ganda.</t>
   </si>
   <si>
-    <t>Memperbaharui baris data pada tabel menu di database server.</t>
-  </si>
-  <si>
     <t>12. Use Case: Mengelola Pengaturan Terminal</t>
   </si>
   <si>
@@ -471,22 +421,32 @@
   </si>
   <si>
     <t>Membuat koneksi socket SPP ke perangkat keras printer dan mengirimkan perintah cetak (byte array) untuk mencetak struk uji coba.</t>
+  </si>
+  <si>
+    <t>Memvalidasi keunikan username kasir, menyimpan data ke database server, mencatat riwayat penambahan/perubahan akun kasir ke tabel audit_logs untuk forensik keamanan, dan menampilkan notifikasi sukses.</t>
+  </si>
+  <si>
+    <t>Memperbarui baris data pada tabel menu atau menu_template di database server, mencatat riwayat perubahan data (nilai sebelum dan sesudah) ke tabel audit_logs untuk forensik keamanan, dan memperbarui katalog menu kasir.</t>
+  </si>
+  <si>
+    <t>Mengunci layar transaksi aktif Kasir Pagi, mengubah status_shift di backend menjadi 'ON_BREAK', mengeset id_user_aktif menjadi NULL, mencatat log kejadian 'BREAK' ke tabel shift_operator_logs, dan menampilkan pop-up login cepat.</t>
+  </si>
+  <si>
+    <t>Memverifikasi ID Kasir Siang, mengubah status_shift kembali menjadi 'OPEN', mengeset id_user_aktif menjadi ID Kasir Siang tanpa menutup/mengubah status shift utama Kasir Pagi di database (shift_session.id_user tetap Kasir Pagi), serta mencatat log kejadian 'SWITCH' ke tabel shift_operator_logs.</t>
+  </si>
+  <si>
+    <t>Setiap transaksi yang diproses mulai detik ini akan dicatat dengan transaksi.id_user = ID Kasir Siang dan transaksi.id_shift = ID Shift Kasir Pagi.</t>
+  </si>
+  <si>
+    <t>Ketika istirahat selesai, Kasir Pagi kembali dan mengulangi proses login cepat untuk mengambil alih kembali operator aktif terminal (id_user_aktif dikembalikan ke Kasir Pagi) serta mencatat log kejadian 'RESUME' ke tabel shift_operator_logs.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -553,10 +513,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -873,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9650499-80B0-4C82-A44A-39E89596DCF0}">
-  <dimension ref="B2:D183"/>
+  <dimension ref="B2:D180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -882,46 +842,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -984,46 +944,46 @@
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
@@ -1082,46 +1042,46 @@
       <c r="D30" s="1"/>
     </row>
     <row r="31" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
@@ -1181,46 +1141,46 @@
       <c r="D44" s="1"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
     </row>
     <row r="51" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
@@ -1273,46 +1233,46 @@
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
     </row>
     <row r="64" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
@@ -1353,47 +1313,47 @@
       </c>
       <c r="D68" s="4"/>
     </row>
-    <row r="69" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:4" ht="195" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
       <c r="D69" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B70" s="2"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="7" t="s">
         <v>54</v>
       </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B73" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-    </row>
-    <row r="74" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="6" t="s">
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B75" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="6" t="s">
@@ -1402,769 +1362,779 @@
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
     </row>
-    <row r="77" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="7" t="s">
+    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B78" s="3"/>
+      <c r="C78" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B79" s="3"/>
-      <c r="C79" s="3" t="s">
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B79" s="2"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D79" s="2"/>
-    </row>
-    <row r="80" spans="2:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="B80" s="2"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3" t="s">
+    </row>
+    <row r="80" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="81" spans="2:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="B81" s="3"/>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B81" s="4"/>
       <c r="C81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="4"/>
+    </row>
+    <row r="82" spans="2:4" ht="195" x14ac:dyDescent="0.25">
+      <c r="B82" s="2"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B84" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D81" s="2"/>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="4"/>
-      <c r="C82" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D82" s="4"/>
-    </row>
-    <row r="83" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B83" s="2"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="4" t="s">
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B85" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="84" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B84" s="2"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="4" t="s">
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="7" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="85" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B87" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-    </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B88" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
     </row>
     <row r="89" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="6" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B91" s="3"/>
+      <c r="C91" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D91" s="2"/>
+    </row>
+    <row r="92" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B92" s="2"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B93" s="3"/>
+      <c r="C93" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D93" s="2"/>
+    </row>
+    <row r="94" spans="2:4" ht="195" x14ac:dyDescent="0.25">
+      <c r="B94" s="4"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B95" s="2"/>
+      <c r="C95" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D95" s="4"/>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B96" s="2"/>
+      <c r="C96" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D96" s="4"/>
+    </row>
+    <row r="97" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B99" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B100" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+    </row>
+    <row r="101" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B102" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-    </row>
-    <row r="91" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-    </row>
-    <row r="92" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-    </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B94" s="3"/>
-      <c r="C94" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D94" s="2"/>
-    </row>
-    <row r="95" spans="2:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="B95" s="2"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="B96" s="3"/>
-      <c r="C96" s="3" t="s">
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+    </row>
+    <row r="103" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D96" s="2"/>
-    </row>
-    <row r="97" spans="2:4" ht="195" x14ac:dyDescent="0.25">
-      <c r="B97" s="4"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="B98" s="2"/>
-      <c r="C98" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D98" s="4"/>
-    </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B99" s="2"/>
-      <c r="C99" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D99" s="4"/>
-    </row>
-    <row r="100" spans="2:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B102" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-    </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B103" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
     </row>
     <row r="104" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B106" s="3"/>
+      <c r="C106" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D106" s="2"/>
+    </row>
+    <row r="107" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B107" s="2"/>
+      <c r="C107" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D107" s="3"/>
+    </row>
+    <row r="108" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B108" s="3"/>
+      <c r="C108" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D108" s="2"/>
+    </row>
+    <row r="109" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B109" s="4"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B110" s="2"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B111" s="2"/>
+      <c r="C111" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D111" s="4"/>
+    </row>
+    <row r="112" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B114" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-    </row>
-    <row r="106" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-    </row>
-    <row r="107" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-    </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B108" s="2" t="s">
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B119" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C121" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D121" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B109" s="3"/>
-      <c r="C109" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D109" s="2"/>
-    </row>
-    <row r="110" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B110" s="2"/>
-      <c r="C110" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D110" s="3"/>
-    </row>
-    <row r="111" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B111" s="3"/>
-      <c r="C111" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D111" s="2"/>
-    </row>
-    <row r="112" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B112" s="4"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="B113" s="2"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B114" s="2"/>
-      <c r="C114" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D114" s="4"/>
-    </row>
-    <row r="115" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B117" s="6" t="s">
+    <row r="122" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B122" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B118" s="6" t="s">
+      <c r="C122" s="3"/>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B123" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B124" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B125" s="4"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>88</v>
+      </c>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B128" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B129" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+    </row>
+    <row r="130" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B130" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B131" s="4"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B134" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-    </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B119" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-    </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B120" s="6" t="s">
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B136" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-    </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B121" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-    </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B122" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-    </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B125" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C125" s="3"/>
-      <c r="D125" s="2"/>
-    </row>
-    <row r="126" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B126" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-    </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B127" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C127" s="3"/>
-      <c r="D127" s="2"/>
-    </row>
-    <row r="128" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B128" s="4"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B129" t="s">
-        <v>92</v>
-      </c>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-    </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B130" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B131" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C131" s="3"/>
-      <c r="D131" s="2"/>
-    </row>
-    <row r="132" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B132" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-    </row>
-    <row r="133" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B133" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C133" s="3"/>
-      <c r="D133" s="2"/>
-    </row>
-    <row r="134" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B134" s="4"/>
-      <c r="C134" s="3"/>
-      <c r="D134" s="4" t="s">
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="135" spans="2:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="B135" s="3"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-    </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B138" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B141" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142" spans="2:4" ht="225" x14ac:dyDescent="0.25">
+      <c r="B142" s="2"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B143" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="2:4" ht="285" x14ac:dyDescent="0.25">
+      <c r="B144" s="4"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B145" s="2"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B146" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D147" s="5"/>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B148" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B149" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B150" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B151" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-    </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B141" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-    </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B142" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-    </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B143" s="2" t="s">
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B152" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B153" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B155" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D155" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B144" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C144" s="3"/>
-      <c r="D144" s="2"/>
-    </row>
-    <row r="145" spans="2:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="B145" s="2"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B146" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C146" s="3"/>
-      <c r="D146" s="2"/>
-    </row>
-    <row r="147" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B147" s="4"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="4" t="s">
+    <row r="156" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B156" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="148" spans="2:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="B148" s="2"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="4" t="s">
+      <c r="C156" s="3"/>
+      <c r="D156" s="2"/>
+    </row>
+    <row r="157" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B157" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="149" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B149" s="3" t="s">
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B158" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D150" s="5"/>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B151" s="6" t="s">
+      <c r="C158" s="3"/>
+      <c r="D158" s="2"/>
+    </row>
+    <row r="159" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B159" s="4"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B152" s="6" t="s">
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>109</v>
+      </c>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B161" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B162" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C162" s="3"/>
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B163" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+    </row>
+    <row r="164" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B165" s="1"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="1"/>
+    </row>
+    <row r="166" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B166" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B167" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-    </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B153" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-    </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B154" s="6" t="s">
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B168" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B169" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-    </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B155" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B156" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-    </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B157" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B158" s="2" t="s">
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B170" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B171" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B172" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C172" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B159" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C159" s="3"/>
-      <c r="D159" s="2"/>
-    </row>
-    <row r="160" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B160" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-    </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B161" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C161" s="3"/>
-      <c r="D161" s="2"/>
-    </row>
-    <row r="162" spans="2:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="B162" s="4"/>
-      <c r="C162" s="3"/>
-      <c r="D162" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B163" t="s">
-        <v>117</v>
-      </c>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-    </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B164" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B165" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C165" s="3"/>
-      <c r="D165" s="2"/>
-    </row>
-    <row r="166" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B166" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-    </row>
-    <row r="167" spans="2:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="B167" s="3"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B168" s="1"/>
-      <c r="C168" s="5"/>
-      <c r="D168" s="1"/>
-    </row>
-    <row r="169" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B169" s="5" t="s">
+    <row r="173" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B173" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C173" s="3"/>
+      <c r="D173" s="2"/>
+    </row>
+    <row r="174" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="B174" s="2"/>
+      <c r="C174" s="4"/>
+      <c r="D174" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B175" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="2"/>
+    </row>
+    <row r="176" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B176" s="4"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B177" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+    </row>
+    <row r="178" spans="2:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="B178" s="3"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B179" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C169" s="5"/>
-      <c r="D169" s="5"/>
-    </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B170" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-    </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B171" s="6" t="s">
+      <c r="C179" s="3"/>
+      <c r="D179" s="4"/>
+    </row>
+    <row r="180" spans="2:4" ht="225" x14ac:dyDescent="0.25">
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-    </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B172" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-    </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B173" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-    </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B174" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-    </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B175" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B176" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C176" s="3"/>
-      <c r="D176" s="2"/>
-    </row>
-    <row r="177" spans="2:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="B177" s="2"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B178" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C178" s="3"/>
-      <c r="D178" s="2"/>
-    </row>
-    <row r="179" spans="2:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="B179" s="4"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B180" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-    </row>
-    <row r="181" spans="2:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="B181" s="3"/>
-      <c r="C181" s="4"/>
-      <c r="D181" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B182" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C182" s="3"/>
-      <c r="D182" s="4"/>
-    </row>
-    <row r="183" spans="2:4" ht="225" x14ac:dyDescent="0.25">
-      <c r="B183" s="3"/>
-      <c r="C183" s="3"/>
-      <c r="D183" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B167:D167"/>
+    <mergeCell ref="B168:D168"/>
+    <mergeCell ref="B169:D169"/>
+    <mergeCell ref="B170:D170"/>
+    <mergeCell ref="B171:D171"/>
+    <mergeCell ref="B150:D150"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="B152:D152"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="B136:D136"/>
+    <mergeCell ref="B137:D137"/>
+    <mergeCell ref="B138:D138"/>
+    <mergeCell ref="B139:D139"/>
+    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="B135:D135"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B46:D46"/>
@@ -2177,51 +2147,20 @@
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B138:D138"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B117:D117"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B137:D137"/>
-    <mergeCell ref="B153:D153"/>
-    <mergeCell ref="B154:D154"/>
-    <mergeCell ref="B155:D155"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="B139:D139"/>
-    <mergeCell ref="B140:D140"/>
-    <mergeCell ref="B141:D141"/>
-    <mergeCell ref="B142:D142"/>
-    <mergeCell ref="B151:D151"/>
-    <mergeCell ref="B152:D152"/>
-    <mergeCell ref="B170:D170"/>
-    <mergeCell ref="B171:D171"/>
-    <mergeCell ref="B172:D172"/>
-    <mergeCell ref="B173:D173"/>
-    <mergeCell ref="B174:D174"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Dokumen/Usecase Scenario.xlsx
+++ b/Dokumen/Usecase Scenario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 7\KP\Point-Of-Sale-App\Dokumen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFB95F3-CF0C-4BB8-BCE2-53E213C4BEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1196F735-C3B6-4186-B56C-25165E58113D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{6A560D3A-8633-4F17-BD07-72BF298389B9}"/>
+    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{6A560D3A-8633-4F17-BD07-72BF298389B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -183,9 +183,6 @@
     <t>Kondisi sebelum: Admin sudah berhasil login ke dalam sistem.</t>
   </si>
   <si>
-    <t>Kondisi sesudah: Perubahan data menu dan harga langsung tersinkronisasi ke database pusat.</t>
-  </si>
-  <si>
     <t>Memilih menu "Kelola Menu" pada dasboard</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
     <t>Kondisi sebelum: Admin sudah berhasil login ke dalam sistem manajemen.</t>
   </si>
   <si>
-    <t>Kondisi sesudah: Perubahan data kasir (tambah baru, edit profil/penempatan cabang, atau hapus akun) tersimpan di database.</t>
-  </si>
-  <si>
     <t>Memilih menu "Kelola Kasir" pada dashboard.</t>
   </si>
   <si>
@@ -439,6 +433,12 @@
   </si>
   <si>
     <t>Ketika istirahat selesai, Kasir Pagi kembali dan mengulangi proses login cepat untuk mengambil alih kembali operator aktif terminal (id_user_aktif dikembalikan ke Kasir Pagi) serta mencatat log kejadian 'RESUME' ke tabel shift_operator_logs.</t>
+  </si>
+  <si>
+    <t>Kondisi sesudah: Perubahan data menu tersimpan, dan data menu yang dihapus terhapus secara logis (soft delete) di database pusat dengan mengisi kolom deleted_at.</t>
+  </si>
+  <si>
+    <t>Kondisi sesudah: Perubahan data kasir tersimpan, dan akun kasir yang dihapus terhapus secara logis (soft delete) sehingga tidak dapat digunakan untuk login lagi.</t>
   </si>
 </sst>
 </file>
@@ -513,10 +513,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -842,46 +842,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
     </row>
     <row r="6" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -944,46 +944,46 @@
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
@@ -1042,46 +1042,46 @@
       <c r="D30" s="1"/>
     </row>
     <row r="31" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
@@ -1141,46 +1141,46 @@
       <c r="D44" s="1"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
     </row>
     <row r="47" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
     </row>
     <row r="49" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
     </row>
     <row r="50" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
@@ -1233,46 +1233,46 @@
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
     </row>
     <row r="60" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
     </row>
     <row r="62" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
     </row>
     <row r="63" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="B63" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
@@ -1288,7 +1288,7 @@
     <row r="65" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1296,20 +1296,20 @@
       <c r="B66" s="2"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="2:4" ht="75" x14ac:dyDescent="0.25">
       <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D68" s="4"/>
     </row>
@@ -1317,50 +1317,50 @@
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
       <c r="D69" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+    </row>
+    <row r="73" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B72" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-    </row>
-    <row r="73" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="7" t="s">
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+    </row>
+    <row r="75" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B74" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-    </row>
-    <row r="75" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
     </row>
     <row r="76" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="B76" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
@@ -1376,7 +1376,7 @@
     <row r="78" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -1384,20 +1384,20 @@
       <c r="B79" s="2"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="2:4" ht="120" x14ac:dyDescent="0.25">
       <c r="B80" s="3"/>
       <c r="C80" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
       <c r="C81" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D81" s="4"/>
     </row>
@@ -1405,50 +1405,50 @@
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
       <c r="D82" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B85" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+    </row>
+    <row r="86" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B87" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+    </row>
+    <row r="88" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-    </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B85" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-    </row>
-    <row r="86" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-    </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B87" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-    </row>
-    <row r="88" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
     </row>
     <row r="89" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
+      <c r="B89" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="2" t="s">
@@ -1464,7 +1464,7 @@
     <row r="91" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -1472,13 +1472,13 @@
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="90" x14ac:dyDescent="0.25">
       <c r="B93" s="3"/>
       <c r="C93" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -1486,20 +1486,20 @@
       <c r="B94" s="4"/>
       <c r="C94" s="3"/>
       <c r="D94" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="2:4" ht="90" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D95" s="4"/>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D96" s="4"/>
     </row>
@@ -1507,50 +1507,50 @@
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B100" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+    </row>
+    <row r="101" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B102" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+    </row>
+    <row r="103" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-    </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B100" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-    </row>
-    <row r="101" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="7" t="s">
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+    </row>
+    <row r="104" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-    </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B102" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-    </row>
-    <row r="103" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-    </row>
-    <row r="104" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="2" t="s">
@@ -1566,21 +1566,21 @@
     <row r="106" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107" spans="2:4" ht="75" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D107" s="3"/>
     </row>
     <row r="108" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -1588,20 +1588,20 @@
       <c r="B109" s="4"/>
       <c r="C109" s="3"/>
       <c r="D109" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="2:4" ht="105" x14ac:dyDescent="0.25">
       <c r="B110" s="2"/>
       <c r="C110" s="3"/>
       <c r="D110" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="111" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B111" s="2"/>
       <c r="C111" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D111" s="4"/>
     </row>
@@ -1609,54 +1609,54 @@
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B114" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B114" s="7" t="s">
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B115" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-    </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B116" s="7" t="s">
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B119" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-    </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B117" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B118" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-    </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B119" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
@@ -1672,21 +1672,21 @@
     </row>
     <row r="122" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B122" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="2"/>
     </row>
     <row r="123" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="2"/>
@@ -1695,12 +1695,12 @@
       <c r="B125" s="4"/>
       <c r="C125" s="3"/>
       <c r="D125" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
@@ -1718,21 +1718,21 @@
     </row>
     <row r="128" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B128" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="2"/>
     </row>
     <row r="129" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
     </row>
     <row r="130" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B130" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="2"/>
@@ -1741,57 +1741,57 @@
       <c r="B131" s="4"/>
       <c r="C131" s="3"/>
       <c r="D131" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="132" spans="2:4" ht="120" x14ac:dyDescent="0.25">
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B134" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B136" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B134" s="7" t="s">
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="6"/>
+      <c r="D137" s="6"/>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-    </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B135" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-    </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B136" s="7" t="s">
+      <c r="C138" s="6"/>
+      <c r="D138" s="6"/>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B139" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-    </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-    </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B138" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-    </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B139" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="2" t="s">
@@ -1806,7 +1806,7 @@
     </row>
     <row r="141" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B141" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="2"/>
@@ -1815,12 +1815,12 @@
       <c r="B142" s="2"/>
       <c r="C142" s="4"/>
       <c r="D142" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="143" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B143" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="2"/>
@@ -1829,19 +1829,19 @@
       <c r="B144" s="4"/>
       <c r="C144" s="3"/>
       <c r="D144" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="145" spans="2:4" ht="120" x14ac:dyDescent="0.25">
       <c r="B145" s="2"/>
       <c r="C145" s="3"/>
       <c r="D145" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="146" spans="2:4" ht="120" x14ac:dyDescent="0.25">
       <c r="B146" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
@@ -1850,50 +1850,50 @@
       <c r="D147" s="5"/>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B149" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C149" s="6"/>
+      <c r="D149" s="6"/>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B150" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6"/>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B151" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="6"/>
+      <c r="D151" s="6"/>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B152" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-    </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B149" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B150" s="7" t="s">
+      <c r="C152" s="6"/>
+      <c r="D152" s="6"/>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B153" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B151" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B152" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-    </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B153" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -1909,21 +1909,21 @@
     </row>
     <row r="156" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B156" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="2"/>
     </row>
     <row r="157" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B157" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="2"/>
@@ -1932,12 +1932,12 @@
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
       <c r="D159" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
@@ -1955,14 +1955,14 @@
     </row>
     <row r="162" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B162" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="2"/>
     </row>
     <row r="163" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B163" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
@@ -1971,7 +1971,7 @@
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
@@ -1981,45 +1981,45 @@
     </row>
     <row r="166" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B166" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6"/>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B169" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169" s="6"/>
+      <c r="D169" s="6"/>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B170" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C170" s="6"/>
+      <c r="D170" s="6"/>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B171" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-    </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B169" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-    </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B170" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-    </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B171" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="2" t="s">
@@ -2034,7 +2034,7 @@
     </row>
     <row r="173" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B173" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="2"/>
@@ -2043,12 +2043,12 @@
       <c r="B174" s="2"/>
       <c r="C174" s="4"/>
       <c r="D174" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="175" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B175" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="2"/>
@@ -2057,12 +2057,12 @@
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
       <c r="D176" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
@@ -2071,12 +2071,12 @@
       <c r="B178" s="3"/>
       <c r="C178" s="4"/>
       <c r="D178" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="179" spans="2:4" ht="60" x14ac:dyDescent="0.25">
       <c r="B179" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="4"/>
@@ -2085,31 +2085,46 @@
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B167:D167"/>
-    <mergeCell ref="B168:D168"/>
-    <mergeCell ref="B169:D169"/>
-    <mergeCell ref="B170:D170"/>
-    <mergeCell ref="B171:D171"/>
-    <mergeCell ref="B150:D150"/>
-    <mergeCell ref="B151:D151"/>
-    <mergeCell ref="B152:D152"/>
-    <mergeCell ref="B153:D153"/>
-    <mergeCell ref="B136:D136"/>
-    <mergeCell ref="B137:D137"/>
-    <mergeCell ref="B138:D138"/>
-    <mergeCell ref="B139:D139"/>
-    <mergeCell ref="B148:D148"/>
-    <mergeCell ref="B149:D149"/>
-    <mergeCell ref="B116:D116"/>
-    <mergeCell ref="B117:D117"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
     <mergeCell ref="B135:D135"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B33:D33"/>
@@ -2126,41 +2141,26 @@
     <mergeCell ref="B84:D84"/>
     <mergeCell ref="B85:D85"/>
     <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="B150:D150"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="B152:D152"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="B136:D136"/>
+    <mergeCell ref="B137:D137"/>
+    <mergeCell ref="B138:D138"/>
+    <mergeCell ref="B139:D139"/>
+    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="B167:D167"/>
+    <mergeCell ref="B168:D168"/>
+    <mergeCell ref="B169:D169"/>
+    <mergeCell ref="B170:D170"/>
+    <mergeCell ref="B171:D171"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
